--- a/railcarfinegoods/railcarfinegoods_5_upgraded_products.xlsx
+++ b/railcarfinegoods/railcarfinegoods_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -628,7 +639,15 @@
       <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>The Railcar Ceramic Mug by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -640,27 +659,27 @@
 Material / BuildHeirloom-Grade Materials with Hand-Finished DetailingApplicationDaily Residential &amp; Commercial Architectural UseCare &amp; MaintenanceWipe clean with soft damp cloth; food-safe / non-porousBrand OriginRailcarfinegoods (United States)Design StandardTimeless Modern Functionalism</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Railcar Ceramic Mug - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Kitchen &amp; Dining</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://railcarfinegoods.com/products/railcar-ceramic-mug</t>
         </is>
@@ -690,7 +709,15 @@
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>The HR Designs Large Wallet - Tan/Skull and Roses by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -702,27 +729,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginRailcarfinegoods (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>HR Designs Large Wallet - Tan/Skull and Roses - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://railcarfinegoods.com/products/hr-designs-large-wallet-tan-skull</t>
         </is>
@@ -752,7 +779,15 @@
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>The HR Designs Small Wallet - Black/American Traditional (Sailor-Mermaid Pinup) by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -764,27 +799,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginRailcarfinegoods (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>HR Designs Small Wallet - Black/American Traditional (Sailor-Mermaid Pinup) - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://railcarfinegoods.com/products/hr-designs-small-wallet-black-american-traditional-skull-serpent</t>
         </is>
@@ -814,7 +849,15 @@
       <c r="E5" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>The Farty Putty by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -826,27 +869,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginRailcarfinegoods (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Farty Putty - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://railcarfinegoods.com/products/farty-putty</t>
         </is>
@@ -876,7 +919,15 @@
       <c r="E6" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>The Mini Colouring Pencils by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -888,27 +939,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginRailcarfinegoods (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Mini Colouring Pencils - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://railcarfinegoods.com/products/mini-colouring-pencils</t>
         </is>
@@ -967,164 +1018,164 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>railcar-ceramic-mug</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Railcar Ceramic Mug | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Railcar Ceramic Mug&lt;/strong&gt; by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1139,141 +1190,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Railcarfinegoods</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Kitchen &amp; Dining</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Kitchen &amp; Dining</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Home Goods, Artisanal Design, Heirloom Quality, Handcrafted, Interior Living, Sustainable Home</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>RAILCAR-CERAMIC-MUG-FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>1900.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0125/0197/5098/files/IMG_5304.jpg?v=1745593759</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
         <is>
           <t>Railcar Ceramic Mug - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>Railcar Ceramic Mug | Handcrafted Artisanal Collection</t>
         </is>
       </c>
-      <c r="AA2" s="11" t="inlineStr">
+      <c r="AA2" s="12" t="inlineStr">
         <is>
           <t>The  Railcar Ceramic Mug  by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered t</t>
         </is>
       </c>
-      <c r="AB2" s="11" t="inlineStr">
+      <c r="AB2" s="12" t="inlineStr">
         <is>
           <t>Home &amp; Garden &gt; Kitchen &amp; Dining</t>
         </is>
       </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>hr-designs-large-wallet-tan-skull</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>HR Designs Large Wallet - Tan/Skull and Roses | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;HR Designs Large Wallet - Tan/Skull and Roses&lt;/strong&gt; by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1288,141 +1339,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Railcarfinegoods</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>HR-DESIGNS-LARGE-WAL-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>4600.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0125/0197/5098/files/35FCA4F5-E14A-4CFE-804A-FC4985570829.jpg?v=1705708161</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
         <is>
           <t>HR Designs Large Wallet - Tan/Skull and Roses - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>HR Designs Large Wallet - Tan/Skull and Roses | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA3" s="11" t="inlineStr">
+      <c r="AA3" s="12" t="inlineStr">
         <is>
           <t>The  HR Designs Large Wallet - Tan/Skull and Roses  by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design.</t>
         </is>
       </c>
-      <c r="AB3" s="11" t="inlineStr">
+      <c r="AB3" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>hr-designs-small-wallet-black-american-traditional-skull-serpent</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>HR Designs Small Wallet - Black/American Traditional (Sailor-Mermaid Pinup) | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;HR Designs Small Wallet - Black/American Traditional (Sailor-Mermaid Pinup)&lt;/strong&gt; by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1437,141 +1488,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Railcarfinegoods</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>HR-DESIGNS-SMALL-WAL-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>3800.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0125/0197/5098/files/7C53BA76-D399-4D4C-BD9A-95FAE76F8A44.jpg?v=1705708185</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
         <is>
           <t>HR Designs Small Wallet - Black/American Traditional (Sailor-Mermaid Pinup) - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>HR Designs Small Wallet - Black/American Traditional (Sailor-Mermaid Pinup) | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
+      <c r="AA4" s="12" t="inlineStr">
         <is>
           <t>The  HR Designs Small Wallet - Black/American Traditional (Sailor-Mermaid Pinup)  by Railcarfinegoods represents the highest standard of intentional crafts</t>
         </is>
       </c>
-      <c r="AB4" s="11" t="inlineStr">
+      <c r="AB4" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>farty-putty</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Farty Putty | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Farty Putty&lt;/strong&gt; by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1586,141 +1637,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Railcarfinegoods</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>FARTY-PUTTY-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>500.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0125/0197/5098/files/FartyPutty.jpg?v=1707176291</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
         <is>
           <t>Farty Putty - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
         <is>
           <t>Farty Putty | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA5" s="11" t="inlineStr">
+      <c r="AA5" s="12" t="inlineStr">
         <is>
           <t>The  Farty Putty  by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to elimin</t>
         </is>
       </c>
-      <c r="AB5" s="11" t="inlineStr">
+      <c r="AB5" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>mini-colouring-pencils</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Mini Colouring Pencils | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Mini Colouring Pencils&lt;/strong&gt; by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1735,124 +1786,124 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Railcarfinegoods</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>MINI-COLOURING-PENCI-FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>500.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0125/0197/5098/files/MiniColouringPencils.jpg?v=1707177553</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>Mini Colouring Pencils - Railcarfinegoods Official Product View</t>
         </is>
       </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
         <is>
           <t>Mini Colouring Pencils | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA6" s="11" t="inlineStr">
+      <c r="AA6" s="12" t="inlineStr">
         <is>
           <t>The  Mini Colouring Pencils  by Railcarfinegoods represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineere</t>
         </is>
       </c>
-      <c r="AB6" s="11" t="inlineStr">
+      <c r="AB6" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
